--- a/tic tac 5.xlsx
+++ b/tic tac 5.xlsx
@@ -1030,17 +1030,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1052,50 +1073,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1104,18 +1108,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1477,10 +1477,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
+      <c r="B1" s="46"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1488,13 +1488,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="59"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -1512,10 +1512,10 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="16.5" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="47"/>
+      <c r="B2" s="51"/>
       <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1523,14 +1523,14 @@
         <v>6</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="64" t="s">
+      <c r="G2" s="51"/>
+      <c r="H2" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="47"/>
+      <c r="I2" s="51"/>
       <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
@@ -1551,10 +1551,10 @@
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="25.5" customHeight="1">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
@@ -1562,14 +1562,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="7"/>
-      <c r="F3" s="65">
+      <c r="F3" s="54">
         <v>46220</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="64" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="47"/>
+      <c r="I3" s="51"/>
       <c r="J3" s="9" t="s">
         <v>14</v>
       </c>
@@ -1620,21 +1620,21 @@
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="47"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="14"/>
       <c r="F5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="48"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="56"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1655,21 +1655,21 @@
       <c r="A6" s="16">
         <v>1</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="47"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="5"/>
       <c r="F6" s="17">
         <v>1</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="48"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="56"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1690,21 +1690,21 @@
       <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="5"/>
       <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="48"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="56"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1725,17 +1725,17 @@
       <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="47"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="5"/>
       <c r="F8" s="17">
         <v>3</v>
       </c>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="48"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="56"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1756,17 +1756,17 @@
       <c r="A9" s="18">
         <v>4</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="50"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="60"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20">
         <v>4</v>
       </c>
-      <c r="G9" s="49"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="52"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="61"/>
       <c r="K9" s="21"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1814,17 +1814,17 @@
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1843,17 +1843,17 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1">
       <c r="A12" s="4"/>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1901,23 +1901,23 @@
       <c r="A14" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="56" t="s">
+      <c r="C14" s="46"/>
+      <c r="D14" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="57"/>
-      <c r="F14" s="56" t="s">
+      <c r="E14" s="46"/>
+      <c r="F14" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="58"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="56" t="s">
+      <c r="G14" s="48"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="59"/>
+      <c r="J14" s="49"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1938,23 +1938,23 @@
       <c r="A15" s="16">
         <v>1</v>
       </c>
-      <c r="B15" s="60" t="s">
+      <c r="B15" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="51"/>
+      <c r="D15" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="45" t="s">
+      <c r="E15" s="51"/>
+      <c r="F15" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="45" t="s">
+      <c r="G15" s="55"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="48"/>
+      <c r="J15" s="56"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1975,23 +1975,23 @@
       <c r="A16" s="16">
         <v>2</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="45" t="s">
+      <c r="C16" s="51"/>
+      <c r="D16" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="45" t="s">
+      <c r="E16" s="51"/>
+      <c r="F16" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="46"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="45" t="s">
+      <c r="G16" s="55"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="48"/>
+      <c r="J16" s="56"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -2012,23 +2012,23 @@
       <c r="A17" s="16">
         <v>3</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="45" t="s">
+      <c r="C17" s="51"/>
+      <c r="D17" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="45" t="s">
+      <c r="E17" s="51"/>
+      <c r="F17" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="46"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="45" t="s">
+      <c r="G17" s="55"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="48"/>
+      <c r="J17" s="56"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -2049,23 +2049,23 @@
       <c r="A18" s="16">
         <v>4</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="45" t="s">
+      <c r="C18" s="51"/>
+      <c r="D18" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="45" t="s">
+      <c r="E18" s="51"/>
+      <c r="F18" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="46"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="45" t="s">
+      <c r="G18" s="55"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="48"/>
+      <c r="J18" s="56"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2086,23 +2086,23 @@
       <c r="A19" s="27">
         <v>5</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="45" t="s">
+      <c r="C19" s="51"/>
+      <c r="D19" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="45" t="s">
+      <c r="E19" s="51"/>
+      <c r="F19" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="46"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="45" t="s">
+      <c r="G19" s="55"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="48"/>
+      <c r="J19" s="56"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2123,23 +2123,23 @@
       <c r="A20" s="27">
         <v>6</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="45" t="s">
+      <c r="C20" s="51"/>
+      <c r="D20" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="45" t="s">
+      <c r="E20" s="51"/>
+      <c r="F20" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="46"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="45" t="s">
+      <c r="G20" s="55"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="48"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2160,23 +2160,23 @@
       <c r="A21" s="27">
         <v>7</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="45" t="s">
+      <c r="C21" s="51"/>
+      <c r="D21" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="45" t="s">
+      <c r="E21" s="51"/>
+      <c r="F21" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="46"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="45" t="s">
+      <c r="G21" s="55"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="J21" s="48"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2197,23 +2197,23 @@
       <c r="A22" s="27">
         <v>8</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="45" t="s">
+      <c r="C22" s="51"/>
+      <c r="D22" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="45" t="s">
+      <c r="E22" s="51"/>
+      <c r="F22" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="46"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="45" t="s">
+      <c r="G22" s="55"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="48"/>
+      <c r="J22" s="56"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2234,15 +2234,15 @@
       <c r="A23" s="27">
         <v>9</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="48"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2263,15 +2263,15 @@
       <c r="A24" s="27">
         <v>10</v>
       </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="48"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="56"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2292,15 +2292,15 @@
       <c r="A25" s="27">
         <v>11</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="48"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="56"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2321,15 +2321,15 @@
       <c r="A26" s="27">
         <v>12</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="48"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="56"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -2350,15 +2350,15 @@
       <c r="A27" s="27">
         <v>13</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="48"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="56"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2379,15 +2379,15 @@
       <c r="A28" s="27">
         <v>14</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="48"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="56"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2408,15 +2408,15 @@
       <c r="A29" s="27">
         <v>15</v>
       </c>
-      <c r="B29" s="45"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="48"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="56"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -2437,15 +2437,15 @@
       <c r="A30" s="27">
         <v>16</v>
       </c>
-      <c r="B30" s="45"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="48"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="56"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -2466,15 +2466,15 @@
       <c r="A31" s="27">
         <v>17</v>
       </c>
-      <c r="B31" s="45"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="48"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="56"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -2495,15 +2495,15 @@
       <c r="A32" s="27">
         <v>18</v>
       </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="48"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="56"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -2524,15 +2524,15 @@
       <c r="A33" s="27">
         <v>19</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="48"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="56"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -2553,15 +2553,15 @@
       <c r="A34" s="28">
         <v>20</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="52"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="61"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -28500,38 +28500,54 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="B25:C25"/>
@@ -28556,54 +28572,38 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B15" r:id="rId1"/>
@@ -28629,30 +28629,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
+      <c r="B1" s="76"/>
       <c r="C1" s="44" t="s">
         <v>63</v>
       </c>
       <c r="D1" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="68"/>
+      <c r="B2" s="76"/>
       <c r="C2" s="36" t="s">
         <v>49</v>
       </c>
@@ -28662,23 +28662,23 @@
       <c r="E2" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="68"/>
-      <c r="H2" s="76" t="s">
+      <c r="G2" s="76"/>
+      <c r="H2" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="68"/>
+      <c r="I2" s="76"/>
       <c r="J2" s="37" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="68"/>
+      <c r="B3" s="76"/>
       <c r="C3" s="34" t="s">
         <v>48</v>
       </c>
@@ -28686,29 +28686,29 @@
         <v>12</v>
       </c>
       <c r="E3" s="38"/>
-      <c r="F3" s="77" t="s">
+      <c r="F3" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="68"/>
-      <c r="H3" s="76" t="s">
+      <c r="G3" s="76"/>
+      <c r="H3" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="68"/>
+      <c r="I3" s="76"/>
       <c r="J3" s="39" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="78"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="40" t="s">
@@ -28717,90 +28717,90 @@
       <c r="B5" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
       <c r="E5" s="33"/>
       <c r="F5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="76" t="s">
+      <c r="G5" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="41">
         <v>1</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="78" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
       <c r="E6" s="34"/>
       <c r="F6" s="41">
         <v>1</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="41">
         <v>2</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
       <c r="E7" s="34"/>
       <c r="F7" s="41">
         <v>2</v>
       </c>
-      <c r="G7" s="67" t="s">
+      <c r="G7" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="76"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="41">
         <v>3</v>
       </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
       <c r="E8" s="34"/>
       <c r="F8" s="41">
         <v>3</v>
       </c>
-      <c r="G8" s="67"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="41">
         <v>4</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
       <c r="E9" s="34"/>
       <c r="F9" s="41">
         <v>4</v>
       </c>
-      <c r="G9" s="67"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="24"/>
@@ -28818,31 +28818,31 @@
       <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="32"/>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" thickBot="1">
       <c r="A13" s="25"/>
@@ -28860,410 +28860,410 @@
       <c r="A14" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="56" t="s">
+      <c r="C14" s="46"/>
+      <c r="D14" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="57"/>
-      <c r="F14" s="56" t="s">
+      <c r="E14" s="46"/>
+      <c r="F14" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="58"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="56" t="s">
+      <c r="G14" s="48"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="59"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="1:10" ht="151.5" customHeight="1">
       <c r="A15" s="27">
         <v>1</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="51"/>
+      <c r="D15" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="48"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="56"/>
     </row>
     <row r="16" spans="1:10" ht="37.5" customHeight="1">
       <c r="A16" s="27">
         <v>2</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="45" t="s">
+      <c r="C16" s="51"/>
+      <c r="D16" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="48"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="56"/>
     </row>
     <row r="17" spans="1:10" ht="32.25" customHeight="1">
       <c r="A17" s="27">
         <v>3</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="45" t="s">
+      <c r="C17" s="51"/>
+      <c r="D17" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="48"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="56"/>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
       <c r="A18" s="27">
         <v>4</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="45" t="s">
+      <c r="C18" s="51"/>
+      <c r="D18" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="48"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="56"/>
     </row>
     <row r="19" spans="1:10" ht="30" customHeight="1">
       <c r="A19" s="27">
         <v>5</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="45" t="s">
+      <c r="C19" s="51"/>
+      <c r="D19" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="48"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="56"/>
     </row>
     <row r="20" spans="1:10" ht="47.25" customHeight="1">
       <c r="A20" s="27">
         <v>6</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="45" t="s">
+      <c r="C20" s="51"/>
+      <c r="D20" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="48"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="56"/>
     </row>
     <row r="21" spans="1:10" ht="51.75" customHeight="1">
       <c r="A21" s="27">
         <v>7</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="45" t="s">
+      <c r="C21" s="51"/>
+      <c r="D21" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="48"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="56"/>
     </row>
     <row r="22" spans="1:10" ht="30.75" customHeight="1">
       <c r="A22" s="27">
         <v>8</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="45" t="s">
+      <c r="C22" s="51"/>
+      <c r="D22" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="48"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="56"/>
     </row>
     <row r="23" spans="1:10" hidden="1">
       <c r="A23" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="48"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="56"/>
     </row>
     <row r="24" spans="1:10" ht="114" customHeight="1">
       <c r="A24" s="27">
         <v>9</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="45" t="s">
+      <c r="C24" s="51"/>
+      <c r="D24" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="48"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="56"/>
     </row>
     <row r="25" spans="1:10" ht="48" customHeight="1">
       <c r="A25" s="27">
         <v>10</v>
       </c>
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="45" t="s">
+      <c r="C25" s="51"/>
+      <c r="D25" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="48"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="56"/>
     </row>
     <row r="26" spans="1:10" ht="46.5" customHeight="1">
       <c r="A26" s="27">
         <v>11</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="45" t="s">
+      <c r="C26" s="51"/>
+      <c r="D26" s="52" t="s">
         <v>79</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="48"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="56"/>
     </row>
     <row r="27" spans="1:10" ht="35.25" customHeight="1">
       <c r="A27" s="27">
         <v>12</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="45" t="s">
+      <c r="C27" s="51"/>
+      <c r="D27" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="48"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="56"/>
     </row>
     <row r="28" spans="1:10" ht="93" customHeight="1">
       <c r="A28" s="27">
         <v>13</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="45" t="s">
+      <c r="C28" s="51"/>
+      <c r="D28" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="71"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="48"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="56"/>
     </row>
     <row r="29" spans="1:10" ht="33" customHeight="1">
       <c r="A29" s="27">
         <v>14</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="45" t="s">
+      <c r="C29" s="51"/>
+      <c r="D29" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="46"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="48"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="82"/>
+      <c r="J29" s="56"/>
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1">
       <c r="A30" s="27">
         <v>15</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="45" t="s">
+      <c r="C30" s="51"/>
+      <c r="D30" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="E30" s="46"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="48"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="82"/>
+      <c r="J30" s="56"/>
     </row>
     <row r="31" spans="1:10" ht="31.5" customHeight="1">
       <c r="A31" s="27">
         <v>16</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="45" t="s">
+      <c r="C31" s="51"/>
+      <c r="D31" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="E31" s="46"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="48"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="78"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="82"/>
+      <c r="J31" s="56"/>
     </row>
     <row r="32" spans="1:10" ht="30" customHeight="1">
       <c r="A32" s="27">
         <v>17</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="45" t="s">
+      <c r="C32" s="51"/>
+      <c r="D32" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="E32" s="46"/>
-      <c r="F32" s="67"/>
-      <c r="G32" s="68"/>
-      <c r="H32" s="68"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="48"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="82"/>
+      <c r="J32" s="56"/>
     </row>
     <row r="33" spans="1:11" ht="32.25" customHeight="1">
       <c r="A33" s="27">
         <v>18</v>
       </c>
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="45" t="s">
+      <c r="C33" s="51"/>
+      <c r="D33" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="46"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="68"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="48"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="82"/>
+      <c r="J33" s="56"/>
     </row>
     <row r="34" spans="1:11" ht="36.75" customHeight="1" thickBot="1">
       <c r="A34" s="27">
         <v>19</v>
       </c>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="50"/>
-      <c r="D34" s="49" t="s">
+      <c r="C34" s="60"/>
+      <c r="D34" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="E34" s="51"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="68"/>
-      <c r="H34" s="68"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="52"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="78"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="61"/>
     </row>
     <row r="35" spans="1:11" ht="33" customHeight="1" thickBot="1">
       <c r="A35" s="27">
         <v>20</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="50"/>
-      <c r="D35" s="49" t="s">
+      <c r="C35" s="60"/>
+      <c r="D35" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="E35" s="50"/>
-      <c r="F35" s="82"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="52"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="74"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="61"/>
     </row>
     <row r="36" spans="1:11" s="29" customFormat="1" ht="47.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A36" s="43">
         <v>21</v>
       </c>
-      <c r="B36" s="71" t="s">
+      <c r="B36" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="73"/>
-      <c r="D36" s="71" t="s">
+      <c r="C36" s="71"/>
+      <c r="D36" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="73"/>
+      <c r="E36" s="71"/>
       <c r="F36" s="42"/>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
@@ -29274,13 +29274,13 @@
       <c r="A37" s="30"/>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="80"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="68"/>
       <c r="K37" s="30"/>
     </row>
     <row r="38" spans="1:11">
@@ -29358,15 +29358,96 @@
     </row>
   </sheetData>
   <mergeCells count="115">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="G5:J5"/>
     <mergeCell ref="B6:D6"/>
@@ -29383,96 +29464,15 @@
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:J35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
